--- a/AAII_Financials/Quarterly/EAXR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EAXR_QTR_FIN.xlsx
@@ -1128,7 +1128,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-200</v>
+        <v>-500</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="E26" s="3">
         <v>-200</v>
@@ -1215,7 +1215,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="E27" s="3">
         <v>-200</v>
@@ -1389,7 +1389,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="E33" s="3">
         <v>-200</v>
@@ -1447,7 +1447,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="E35" s="3">
         <v>-200</v>
@@ -1913,7 +1913,7 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="E54" s="3">
         <v>3700</v>
@@ -1968,7 +1968,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="E57" s="3">
         <v>1200</v>
@@ -2387,7 +2387,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-3700</v>
+        <v>-3400</v>
       </c>
       <c r="E72" s="3">
         <v>-2600</v>
@@ -2503,7 +2503,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="E76" s="3">
         <v>500</v>
@@ -2595,7 +2595,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="E81" s="3">
         <v>-200</v>
